--- a/data/employees/EMP036/AST-EMP036-06.xlsx
+++ b/data/employees/EMP036/AST-EMP036-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,166 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Budget Tracker - Avery Wilson (Finance)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Avery Wilson | Role: Analyst | Location: Fremont | Date: 2025-02-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp036 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>93</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp036 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>74</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Cost Centre</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Budget ($K)</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Actual ($K)</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Variance ($K)</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Variance %</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Status</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp036 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>68</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CC-1001 Engineering</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2500</v>
-      </c>
-      <c r="C5" t="n">
-        <v>2380</v>
-      </c>
-      <c r="D5" t="n">
-        <v>120</v>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ast Emp036 06</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-W04</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
       </c>
       <c r="E5" t="n">
-        <v>4.8</v>
+        <v>78</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Section 1: Customer escalation analysis. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CC-1002 Operations</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1800</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1920</v>
-      </c>
-      <c r="D6" t="n">
-        <v>-120</v>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ast Emp036 06</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-W05</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
       </c>
       <c r="E6" t="n">
-        <v>-6.7</v>
+        <v>64</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Section 1: Automation backlog refinement. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CC-1003 R&amp;D</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>3200</v>
-      </c>
-      <c r="C7" t="n">
-        <v>3100</v>
-      </c>
-      <c r="D7" t="n">
-        <v>100</v>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ast Emp036 06</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-W06</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
       </c>
       <c r="E7" t="n">
-        <v>3.1</v>
+        <v>63</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Section 1: Knowledge transfer and onboarding. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CC-1004 IT</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1200</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1195</v>
-      </c>
-      <c r="D8" t="n">
-        <v>5</v>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ast Emp036 06</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-W07</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
       </c>
       <c r="E8" t="n">
-        <v>0.4</v>
+        <v>94</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>On Track</t>
+          <t>Section 1: Fabric semantic model planning. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp036 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>87</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp036 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>84</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp036 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>97</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp036 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>87</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp036 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>93</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp036 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>95</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp036 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>63</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp036 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>97</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp036 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>95</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp036 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>94</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp036 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>85</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp036 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>82</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp036 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>71</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp036 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>81</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp036 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>68</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp036 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>70</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp036 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>95</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP036</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP036 contributes to ast emp036 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>